--- a/data/trans_dic/P57_AC_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,52; 77,95</t>
+          <t>71,48; 78,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,07; 65,29</t>
+          <t>57,71; 65,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,76; 81,22</t>
+          <t>74,9; 81,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,51; 62,43</t>
+          <t>53,07; 62,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,85; 79,06</t>
+          <t>72,41; 79,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,72; 73,81</t>
+          <t>66,41; 73,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,31; 86,0</t>
+          <t>79,81; 85,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,55; 65,03</t>
+          <t>58,55; 65,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,02; 77,59</t>
+          <t>73,06; 77,55</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,21; 68,54</t>
+          <t>63,39; 68,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,5; 82,75</t>
+          <t>78,69; 82,79</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>57,22; 62,62</t>
+          <t>56,99; 62,56</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,31; 70,63</t>
+          <t>64,41; 70,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,65; 68,64</t>
+          <t>63,0; 68,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,88; 79,16</t>
+          <t>73,82; 79,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,03; 65,05</t>
+          <t>26,1; 64,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,36; 75,43</t>
+          <t>69,81; 75,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,11; 75,99</t>
+          <t>70,08; 75,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,76; 85,28</t>
+          <t>80,74; 85,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,54; 68,87</t>
+          <t>63,33; 68,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,08; 72,13</t>
+          <t>67,97; 72,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,37; 71,6</t>
+          <t>67,43; 71,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,06; 81,69</t>
+          <t>78,04; 81,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>39,08; 65,62</t>
+          <t>38,31; 65,58</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,88; 65,58</t>
+          <t>58,05; 65,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,74; 67,21</t>
+          <t>59,3; 67,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,47; 86,38</t>
+          <t>80,7; 86,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,68; 68,49</t>
+          <t>59,66; 68,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,76; 68,72</t>
+          <t>61,88; 68,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,75; 71,66</t>
+          <t>64,79; 71,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>80,72; 86,37</t>
+          <t>81,01; 86,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,68; 65,44</t>
+          <t>52,03; 65,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,09; 66,31</t>
+          <t>60,92; 65,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,36; 68,48</t>
+          <t>63,26; 68,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81,44; 85,61</t>
+          <t>81,55; 85,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,41; 65,7</t>
+          <t>56,74; 65,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,8; 70,77</t>
+          <t>64,7; 70,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,19; 75,27</t>
+          <t>69,46; 75,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75,68; 81,16</t>
+          <t>76,16; 81,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,73; 62,09</t>
+          <t>54,61; 62,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,22; 71,87</t>
+          <t>66,07; 71,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,29; 81,38</t>
+          <t>76,23; 81,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,25; 81,56</t>
+          <t>76,42; 81,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43,09; 60,62</t>
+          <t>45,03; 60,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,51; 70,52</t>
+          <t>66,53; 70,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>73,83; 77,73</t>
+          <t>74,06; 77,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>77,03; 80,57</t>
+          <t>76,97; 80,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,41; 60,09</t>
+          <t>50,66; 60,13</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,31; 69,51</t>
+          <t>66,37; 69,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,6; 68,03</t>
+          <t>64,68; 67,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,55; 80,41</t>
+          <t>77,61; 80,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,97; 61,91</t>
+          <t>43,84; 61,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,09; 72,13</t>
+          <t>69,12; 72,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,68; 74,62</t>
+          <t>71,8; 74,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,87; 83,32</t>
+          <t>80,77; 83,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,56; 63,26</t>
+          <t>56,74; 63,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,49</t>
+          <t>68,26; 70,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68,72; 70,99</t>
+          <t>68,67; 70,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,66; 81,6</t>
+          <t>79,7; 81,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,74; 61,7</t>
+          <t>51,79; 61,75</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke)</t>
+          <t>Población con apoyo confidencial bajo (Duke) (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>496378; 540950</t>
+          <t>496080; 542960</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>405207; 455635</t>
+          <t>402676; 455051</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>502851; 546309</t>
+          <t>503819; 547481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>337033; 393204</t>
+          <t>334289; 393082</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>501458; 544204</t>
+          <t>498458; 544608</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>463144; 512410</t>
+          <t>461011; 513410</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>538068; 576154</t>
+          <t>534675; 575447</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>386845; 429645</t>
+          <t>386820; 431261</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1009402; 1072555</t>
+          <t>1009906; 1072069</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>879945; 954139</t>
+          <t>882372; 955408</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1054010; 1111023</t>
+          <t>1056548; 1111498</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>738470; 808162</t>
+          <t>735417; 807426</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>617804; 678536</t>
+          <t>618806; 675483</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>631720; 692145</t>
+          <t>635185; 694423</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>752342; 806088</t>
+          <t>751709; 808771</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>331826; 770058</t>
+          <t>309035; 766186</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>670877; 729637</t>
+          <t>675240; 729738</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>720832; 781264</t>
+          <t>720513; 778645</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>839871; 886873</t>
+          <t>839626; 890284</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>602083; 652587</t>
+          <t>600150; 651886</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1312626; 1390552</t>
+          <t>1310389; 1392877</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1372000; 1458049</t>
+          <t>1373223; 1457010</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1606670; 1681533</t>
+          <t>1606270; 1683892</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>833059; 1398601</t>
+          <t>816545; 1397766</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>392699; 444977</t>
+          <t>393899; 446121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>448231; 504298</t>
+          <t>444974; 506777</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>604903; 649349</t>
+          <t>606641; 647912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>416982; 478486</t>
+          <t>416787; 477995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>422353; 469907</t>
+          <t>423148; 468938</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>501028; 554515</t>
+          <t>501287; 554384</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>626173; 669987</t>
+          <t>628404; 670433</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>372887; 472125</t>
+          <t>375365; 472534</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>832271; 903381</t>
+          <t>829903; 898209</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>965637; 1043681</t>
+          <t>964089; 1043129</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1243908; 1307597</t>
+          <t>1245641; 1305886</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>815294; 933093</t>
+          <t>805862; 932733</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>609549; 665668</t>
+          <t>608594; 663045</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>652199; 709492</t>
+          <t>654745; 711408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>707005; 758235</t>
+          <t>711487; 760404</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>501323; 568819</t>
+          <t>500287; 568636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>687155; 745708</t>
+          <t>685603; 744023</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>795082; 848113</t>
+          <t>794413; 848920</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>789930; 844935</t>
+          <t>791719; 843961</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>464514; 653544</t>
+          <t>485438; 656680</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1315739; 1395058</t>
+          <t>1316175; 1395635</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1465327; 1542739</t>
+          <t>1469872; 1546402</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1517641; 1587517</t>
+          <t>1516486; 1589244</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>985381; 1198279</t>
+          <t>1010207; 1199175</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2170969; 2275537</t>
+          <t>2172811; 2281084</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2195742; 2312300</t>
+          <t>2198487; 2310203</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2618813; 2715505</t>
+          <t>2620694; 2717371</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1473323; 2122379</t>
+          <t>1502962; 2115993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2333250; 2435811</t>
+          <t>2334164; 2444053</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2536064; 2640140</t>
+          <t>2540611; 2644727</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2847958; 2934358</t>
+          <t>2844493; 2937690</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1927645; 2155887</t>
+          <t>1933782; 2152435</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4539778; 4688116</t>
+          <t>4540249; 4681898</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4767294; 4924822</t>
+          <t>4763531; 4918237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5495187; 5628988</t>
+          <t>5497943; 5625830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3468951; 4218069</t>
+          <t>3540564; 4221190</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P57_AC_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P57_AC_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,48; 78,23</t>
+          <t>71,54; 77,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,71; 65,21</t>
+          <t>57,98; 65,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,9; 81,39</t>
+          <t>74,83; 81,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53,07; 62,41</t>
+          <t>54,5; 62,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,41; 79,12</t>
+          <t>72,27; 79,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,41; 73,96</t>
+          <t>66,84; 73,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,81; 85,89</t>
+          <t>80,37; 85,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>58,55; 65,28</t>
+          <t>58,7; 65,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,06; 77,55</t>
+          <t>73,26; 77,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,39; 68,64</t>
+          <t>63,53; 68,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78,69; 82,79</t>
+          <t>78,52; 82,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>56,99; 62,56</t>
+          <t>57,94; 63,2</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,41; 70,31</t>
+          <t>64,7; 70,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,0; 68,87</t>
+          <t>62,61; 69,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,82; 79,42</t>
+          <t>73,83; 79,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,1; 64,72</t>
+          <t>61,01; 67,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>69,81; 75,45</t>
+          <t>69,83; 75,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,08; 75,74</t>
+          <t>70,12; 75,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,74; 85,61</t>
+          <t>80,68; 85,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,33; 68,79</t>
+          <t>64,68; 69,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>67,97; 72,25</t>
+          <t>67,92; 72,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,43; 71,55</t>
+          <t>67,5; 71,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,04; 81,81</t>
+          <t>78,01; 81,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,31; 65,58</t>
+          <t>63,84; 68,06</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,05; 65,75</t>
+          <t>58,11; 65,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,3; 67,54</t>
+          <t>59,96; 67,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,7; 86,19</t>
+          <t>80,73; 86,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,66; 68,42</t>
+          <t>61,01; 69,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,88; 68,57</t>
+          <t>61,58; 68,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,79; 71,65</t>
+          <t>64,17; 71,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,01; 86,42</t>
+          <t>81,05; 86,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,03; 65,49</t>
+          <t>61,34; 67,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,92; 65,93</t>
+          <t>60,9; 66,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63,26; 68,44</t>
+          <t>63,49; 68,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81,55; 85,49</t>
+          <t>81,71; 85,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>56,74; 65,68</t>
+          <t>62,22; 67,41</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>60,67%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,7; 70,49</t>
+          <t>64,91; 70,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,46; 75,48</t>
+          <t>69,32; 75,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76,16; 81,39</t>
+          <t>76,04; 81,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,61; 62,07</t>
+          <t>56,68; 63,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,07; 71,7</t>
+          <t>66,14; 71,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,23; 81,46</t>
+          <t>76,75; 81,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,42; 81,46</t>
+          <t>76,18; 81,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,03; 60,91</t>
+          <t>58,6; 63,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,53; 70,55</t>
+          <t>66,51; 70,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74,06; 77,92</t>
+          <t>73,95; 77,88</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>76,97; 80,66</t>
+          <t>76,99; 80,71</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,66; 60,13</t>
+          <t>58,53; 62,73</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,37; 69,67</t>
+          <t>66,57; 69,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,68; 67,97</t>
+          <t>64,64; 67,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77,61; 80,47</t>
+          <t>77,74; 80,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43,84; 61,72</t>
+          <t>60,61; 64,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,12; 72,37</t>
+          <t>69,18; 72,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,8; 74,75</t>
+          <t>71,74; 74,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,77; 83,42</t>
+          <t>80,88; 83,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>56,74; 63,16</t>
+          <t>62,44; 65,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,26; 70,39</t>
+          <t>68,15; 70,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68,67; 70,9</t>
+          <t>68,75; 70,93</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79,7; 81,55</t>
+          <t>79,62; 81,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,79; 61,75</t>
+          <t>62,04; 64,4</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>366201</t>
+          <t>404045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>407975</t>
+          <t>445842</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>774177</t>
+          <t>849887</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>496080; 542960</t>
+          <t>496467; 541088</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>402676; 455051</t>
+          <t>404591; 455042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>503819; 547481</t>
+          <t>503349; 547892</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>334289; 393082</t>
+          <t>373099; 430516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>498458; 544608</t>
+          <t>497478; 544693</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>461011; 513410</t>
+          <t>463991; 511118</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>534675; 575447</t>
+          <t>538437; 575579</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>386820; 431261</t>
+          <t>421252; 467396</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1009906; 1072069</t>
+          <t>1012738; 1074185</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>882372; 955408</t>
+          <t>884336; 955736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1056548; 1111498</t>
+          <t>1054250; 1113699</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>735417; 807426</t>
+          <t>812404; 886151</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>598455</t>
+          <t>671284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>626716</t>
+          <t>713274</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1225171</t>
+          <t>1384559</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>618806; 675483</t>
+          <t>621550; 678478</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>635185; 694423</t>
+          <t>631273; 696741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>751709; 808771</t>
+          <t>751860; 805565</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>309035; 766186</t>
+          <t>633116; 703672</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>675240; 729738</t>
+          <t>675417; 729311</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>720513; 778645</t>
+          <t>720867; 779546</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>839626; 890284</t>
+          <t>839030; 885024</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>600150; 651886</t>
+          <t>684687; 740068</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1310389; 1392877</t>
+          <t>1309482; 1393894</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1373223; 1457010</t>
+          <t>1374545; 1457143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1606270; 1683892</t>
+          <t>1605696; 1678775</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>816545; 1397766</t>
+          <t>1338383; 1426802</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>447636</t>
+          <t>518495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>441556</t>
+          <t>519314</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>889191</t>
+          <t>1037809</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>393899; 446121</t>
+          <t>394282; 444750</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>444974; 506777</t>
+          <t>449881; 506673</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>606641; 647912</t>
+          <t>606843; 647827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>416787; 477995</t>
+          <t>484790; 550864</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>423148; 468938</t>
+          <t>421110; 469488</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>501287; 554384</t>
+          <t>496509; 552326</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>628404; 670433</t>
+          <t>628716; 670175</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>375365; 472534</t>
+          <t>492765; 543660</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>829903; 898209</t>
+          <t>829624; 901313</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>964089; 1043129</t>
+          <t>967649; 1041813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1245641; 1305886</t>
+          <t>1248096; 1306016</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>805862; 932733</t>
+          <t>994291; 1077091</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>536323</t>
+          <t>589820</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>604981</t>
+          <t>673503</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1141304</t>
+          <t>1263324</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>608594; 663045</t>
+          <t>610593; 664822</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>654745; 711408</t>
+          <t>653425; 709600</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>711487; 760404</t>
+          <t>710433; 758745</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>500287; 568636</t>
+          <t>555152; 623028</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>685603; 744023</t>
+          <t>686248; 746316</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>794413; 848920</t>
+          <t>799826; 851864</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>791719; 843961</t>
+          <t>789272; 845844</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>485438; 656680</t>
+          <t>646204; 703359</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1316175; 1395635</t>
+          <t>1315721; 1394510</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1469872; 1546402</t>
+          <t>1467744; 1545606</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1516486; 1589244</t>
+          <t>1516819; 1590253</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1010207; 1199175</t>
+          <t>1218711; 1306104</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1948615</t>
+          <t>2183645</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2081228</t>
+          <t>2351934</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4029843</t>
+          <t>4535579</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2172811; 2281084</t>
+          <t>2179290; 2280419</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2198487; 2310203</t>
+          <t>2197132; 2310843</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2620694; 2717371</t>
+          <t>2625373; 2718147</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1502962; 2115993</t>
+          <t>2119131; 2243836</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2334164; 2444053</t>
+          <t>2336294; 2438619</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2540611; 2644727</t>
+          <t>2538399; 2645490</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2844493; 2937690</t>
+          <t>2848419; 2940170</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1933782; 2152435</t>
+          <t>2299379; 2411260</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4540249; 4681898</t>
+          <t>4532346; 4684354</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4763531; 4918237</t>
+          <t>4769576; 4920842</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5497943; 5625830</t>
+          <t>5492814; 5627169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3540564; 4221190</t>
+          <t>4453342; 4622930</t>
         </is>
       </c>
     </row>
